--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.98391756703935</v>
+        <v>2.434886604643895</v>
       </c>
       <c r="D2" t="n">
-        <v>15.24939589637034</v>
+        <v>2.47802683316018</v>
       </c>
       <c r="E2" t="n">
-        <v>11.35303030833345</v>
+        <v>1.844867425104186</v>
       </c>
       <c r="F2" t="n">
-        <v>11.25793806742239</v>
+        <v>1.829414935956138</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.89378665588793</v>
+        <v>2.420240331581789</v>
       </c>
       <c r="D3" t="n">
-        <v>13.88500484876181</v>
+        <v>2.256313287923795</v>
       </c>
       <c r="E3" t="n">
-        <v>11.35303030833345</v>
+        <v>1.844867425104186</v>
       </c>
       <c r="F3" t="n">
-        <v>11.25793806742239</v>
+        <v>1.829414935956138</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.14948124668684</v>
+        <v>3.599290702586611</v>
       </c>
       <c r="D4" t="n">
-        <v>21.5593271876743</v>
+        <v>3.503390667997074</v>
       </c>
       <c r="E4" t="n">
-        <v>11.35303030833345</v>
+        <v>1.844867425104186</v>
       </c>
       <c r="F4" t="n">
-        <v>11.25793806742239</v>
+        <v>1.829414935956138</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.69422219791564</v>
+        <v>5.637811107161292</v>
       </c>
       <c r="D5" t="n">
-        <v>33.67251214067037</v>
+        <v>5.471783222858935</v>
       </c>
       <c r="E5" t="n">
-        <v>11.35303030833345</v>
+        <v>1.844867425104186</v>
       </c>
       <c r="F5" t="n">
-        <v>11.25793806742239</v>
+        <v>1.829414935956138</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>51.6919205756967</v>
+        <v>8.399937093550713</v>
       </c>
       <c r="D6" t="n">
-        <v>50.72391636561614</v>
+        <v>8.242636409412624</v>
       </c>
       <c r="E6" t="n">
-        <v>11.35303030833345</v>
+        <v>1.844867425104186</v>
       </c>
       <c r="F6" t="n">
-        <v>11.25793806742239</v>
+        <v>1.829414935956138</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.05565334385919</v>
+        <v>6.834043668377118</v>
       </c>
       <c r="D7" t="n">
-        <v>41.93380970738018</v>
+        <v>6.81424407744928</v>
       </c>
       <c r="E7" t="n">
-        <v>11.35303030833345</v>
+        <v>1.844867425104186</v>
       </c>
       <c r="F7" t="n">
-        <v>11.25793806742239</v>
+        <v>1.829414935956138</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.60590156312429</v>
+        <v>5.135959004007698</v>
       </c>
       <c r="D8" t="n">
-        <v>30.79721065913137</v>
+        <v>5.004546732108847</v>
       </c>
       <c r="E8" t="n">
-        <v>11.35303030833345</v>
+        <v>1.844867425104186</v>
       </c>
       <c r="F8" t="n">
-        <v>11.25793806742239</v>
+        <v>1.829414935956138</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>32.32893641223115</v>
+        <v>5.253452166987563</v>
       </c>
       <c r="D9" t="n">
-        <v>32.02378884046244</v>
+        <v>5.203865686575146</v>
       </c>
       <c r="E9" t="n">
-        <v>11.35303030833345</v>
+        <v>1.844867425104186</v>
       </c>
       <c r="F9" t="n">
-        <v>11.25793806742239</v>
+        <v>1.829414935956138</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.72107227325179</v>
+        <v>5.154674244403415</v>
       </c>
       <c r="D10" t="n">
-        <v>31.49556403300739</v>
+        <v>5.118029155363701</v>
       </c>
       <c r="E10" t="n">
-        <v>11.35303030833345</v>
+        <v>1.844867425104186</v>
       </c>
       <c r="F10" t="n">
-        <v>11.25793806742239</v>
+        <v>1.829414935956138</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
